--- a/Báo cáo hàng tuần.xlsx
+++ b/Báo cáo hàng tuần.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/73515ac4d74bce43/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="9" documentId="8_{9EB2EF27-5564-4761-BBD8-EE712223C93D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F6094BD-29BF-4ACF-A9CF-96809193A80A}"/>
@@ -145,13 +145,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -507,7 +507,7 @@
       <c r="N1" s="1"/>
     </row>
     <row r="2" spans="6:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="7" t="s">
         <v>1</v>
       </c>
       <c r="G2" s="3" t="s">
@@ -515,19 +515,19 @@
       </c>
     </row>
     <row r="3" spans="6:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F3" s="5"/>
-      <c r="G3" s="6" t="s">
+      <c r="F3" s="7"/>
+      <c r="G3" s="5" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="6:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F4" s="5"/>
+      <c r="F4" s="7"/>
       <c r="G4" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="6:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="7" t="s">
         <v>5</v>
       </c>
       <c r="G5" s="2" t="s">
@@ -535,67 +535,67 @@
       </c>
     </row>
     <row r="6" spans="6:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F6" s="5"/>
+      <c r="F6" s="7"/>
       <c r="G6" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="6:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F7" s="5"/>
+      <c r="F7" s="7"/>
       <c r="G7" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="6:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G8" s="7"/>
+      <c r="G8" s="6"/>
     </row>
     <row r="9" spans="6:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G9" s="7"/>
+      <c r="G9" s="6"/>
     </row>
     <row r="10" spans="6:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G10" s="7"/>
+      <c r="G10" s="6"/>
     </row>
     <row r="11" spans="6:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G11" s="7"/>
+      <c r="G11" s="6"/>
     </row>
     <row r="12" spans="6:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G12" s="7"/>
+      <c r="G12" s="6"/>
     </row>
     <row r="13" spans="6:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G13" s="7"/>
+      <c r="G13" s="6"/>
     </row>
     <row r="14" spans="6:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G14" s="7"/>
+      <c r="G14" s="6"/>
     </row>
     <row r="15" spans="6:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G15" s="7"/>
+      <c r="G15" s="6"/>
     </row>
     <row r="16" spans="6:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G16" s="7"/>
+      <c r="G16" s="6"/>
     </row>
     <row r="17" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G17" s="7"/>
+      <c r="G17" s="6"/>
     </row>
     <row r="18" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G18" s="7"/>
+      <c r="G18" s="6"/>
     </row>
     <row r="19" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G19" s="7"/>
+      <c r="G19" s="6"/>
     </row>
     <row r="20" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G20" s="7"/>
+      <c r="G20" s="6"/>
     </row>
     <row r="21" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G21" s="7"/>
+      <c r="G21" s="6"/>
     </row>
     <row r="22" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G22" s="7"/>
+      <c r="G22" s="6"/>
     </row>
     <row r="23" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G23" s="7"/>
+      <c r="G23" s="6"/>
     </row>
     <row r="24" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G24" s="7"/>
+      <c r="G24" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="2">
